--- a/04_Figures/F07/c_data/F07_supplementary.xlsx
+++ b/04_Figures/F07/c_data/F07_supplementary.xlsx
@@ -28827,7 +28827,7 @@
     <col min="6" max="6" width="3.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="5.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="6.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28885,7 +28885,7 @@
         <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.11</v>
+        <v>0.118811881188119</v>
       </c>
     </row>
     <row r="3">
@@ -28914,7 +28914,7 @@
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05</v>
+        <v>0.0594059405940594</v>
       </c>
     </row>
     <row r="4">
@@ -28943,7 +28943,7 @@
         <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>0.92</v>
+        <v>0.920792079207921</v>
       </c>
     </row>
     <row r="5">
@@ -28972,7 +28972,7 @@
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.044</v>
+        <v>0.044955044955045</v>
       </c>
     </row>
   </sheetData>
@@ -29677,7 +29677,7 @@
         <v>0.92</v>
       </c>
       <c r="C2" t="n">
-        <v>0.044</v>
+        <v>0.044955044955045</v>
       </c>
       <c r="D2" t="n">
         <v>0.64428</v>
